--- a/data/Music.xlsx
+++ b/data/Music.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\채아_SALT\2026_S\Music\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43F081F-7BCD-4300-A80C-88AB7D465232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8326E93-DBC0-4380-97E8-74C828053D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E435C2E-1A91-4033-A76C-5E5C4417E09B}"/>
   </bookViews>
@@ -38,69 +38,36 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
-    <t>Overtone</t>
-  </si>
-  <si>
     <t>A fundamental pitch with resultant pitches sounding above it according to the overtone series.</t>
   </si>
   <si>
-    <t>Timbre</t>
-  </si>
-  <si>
     <t>The tone color of a sound resulting from the overtones.</t>
   </si>
   <si>
-    <t>Pitch</t>
-  </si>
-  <si>
     <t>The frequency of the note's vibration (note names like C, D, E).</t>
   </si>
   <si>
-    <t>Amplitude</t>
-  </si>
-  <si>
     <t>How loud or soft a sound is.</t>
   </si>
   <si>
-    <t>Duration</t>
-  </si>
-  <si>
     <t>How long or short the sound is.</t>
   </si>
   <si>
-    <t>Melody</t>
-  </si>
-  <si>
     <t>A succession of musical notes; a series of pitches often organized into phrases.</t>
   </si>
   <si>
-    <t>Harmony</t>
-  </si>
-  <si>
     <t>The simultaneous, vertical combination of notes, usually forming chords.</t>
   </si>
   <si>
-    <t>Rhythm</t>
-  </si>
-  <si>
     <t>The organization of music in time; closely related to meter.</t>
   </si>
   <si>
-    <t>Texture</t>
-  </si>
-  <si>
     <t>The density (thickness or thinness) of layers of sounds, melodies, and rhythms in a piece.</t>
   </si>
   <si>
-    <t>Monophony</t>
-  </si>
-  <si>
     <t>A single layer of sound; e.g., a solo voice.</t>
   </si>
   <si>
-    <t>Homophony</t>
-  </si>
-  <si>
     <t>A melody with an accompaniment; e.g., a lead singer and a band.</t>
   </si>
   <si>
@@ -110,93 +77,48 @@
     <t>Two or more independent voices; e.g., a round or fugue.</t>
   </si>
   <si>
-    <t>Structure/Form</t>
-  </si>
-  <si>
     <t>The sections or movements of a piece (verse and refrain, ABA, Rondo, etc.).</t>
   </si>
   <si>
-    <t>Dynamics</t>
-  </si>
-  <si>
     <t>Volume (amplitude)—how loud, soft, medium, or gradually changing (crescendo).</t>
   </si>
   <si>
-    <t>Tempo</t>
-  </si>
-  <si>
     <t>Beats per minute; how fast, medium, or slow a piece of music is played.</t>
   </si>
   <si>
-    <t>Articulation</t>
-  </si>
-  <si>
     <t>The manner in which notes are played (staccato: short, legato: smooth, marcato: stressed).</t>
   </si>
   <si>
-    <t>Religious music</t>
-  </si>
-  <si>
     <t>Music composed for use in religious ceremonies and rituals, connected to spiritual beliefs.</t>
   </si>
   <si>
-    <t>Healing songs</t>
-  </si>
-  <si>
     <t>Music used to support physical, emotional, or spiritual healing in therapeutic contexts.</t>
   </si>
   <si>
-    <t>Pop Music</t>
-  </si>
-  <si>
     <t>A genre of popular music that originated in the West during the 1950s and 1960s.</t>
   </si>
   <si>
-    <t>Entertainment Music</t>
-  </si>
-  <si>
     <t>Music created primarily for enjoyment and leisure, commonly experienced through concerts.</t>
   </si>
   <si>
-    <t>Dance Music</t>
-  </si>
-  <si>
     <t>Music specifically created to accompany dancing with a strong, steady beat.</t>
   </si>
   <si>
-    <t>Festival/Party Music</t>
-  </si>
-  <si>
     <t>Music used to enhance social events and create an energetic and celebratory atmosphere.</t>
   </si>
   <si>
-    <t>Work song</t>
-  </si>
-  <si>
     <t>Traditional folk songs sung by workers to match the pace of physical labor.</t>
   </si>
   <si>
-    <t>Commercial Songs</t>
-  </si>
-  <si>
     <t>Music used in advertisements to promote products and services effectively.</t>
   </si>
   <si>
-    <t>Military Music</t>
-  </si>
-  <si>
     <t>Music composed for ceremonies, marching, and signaling events in military contexts.</t>
   </si>
   <si>
-    <t>Film music</t>
-  </si>
-  <si>
     <t>Music used in a film to accompany action, enhance emotional impact, and create atmosphere.</t>
   </si>
   <si>
-    <t>Musical Theatre</t>
-  </si>
-  <si>
     <t>A form of theatre that combines music, songs, spoken dialogue, acting, and dance.</t>
   </si>
   <si>
@@ -247,6 +169,110 @@
   </si>
   <si>
     <t>Definition</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>homophony</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>monophony</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>texture</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rhythm</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>harmony</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>melody</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>amplitude</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pitch</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>timbre</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>overtone</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>structure/form</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dynamics</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tempo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>articulation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>religious music</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>healing songs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pop music</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>entertainment music</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dance music</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>festival/party music</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>work song</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>commercial songs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>military music</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>film music</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>musical theatre</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -700,282 +726,282 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.5">
       <c r="A2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="28.5">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="28.5">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="28.5">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
